--- a/artfynd/A 4168-2025 artfynd.xlsx
+++ b/artfynd/A 4168-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129954629</v>
       </c>
       <c r="B2" t="n">
-        <v>96111</v>
+        <v>96112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4168-2025 artfynd.xlsx
+++ b/artfynd/A 4168-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129954629</v>
       </c>
       <c r="B2" t="n">
-        <v>96112</v>
+        <v>96129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4168-2025 artfynd.xlsx
+++ b/artfynd/A 4168-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129954629</v>
       </c>
       <c r="B2" t="n">
-        <v>96145</v>
+        <v>96147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4168-2025 artfynd.xlsx
+++ b/artfynd/A 4168-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129954629</v>
       </c>
       <c r="B2" t="n">
-        <v>96147</v>
+        <v>96234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4168-2025 artfynd.xlsx
+++ b/artfynd/A 4168-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129954629</v>
+        <v>206438</v>
       </c>
       <c r="B2" t="n">
-        <v>96234</v>
+        <v>83304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alboryds gamla tomt, Alboryds gamla tomt, Ög</t>
+          <t>200 m SO Knäpperyds gla tomt (08E0h37), Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483508</v>
+        <v>483471</v>
       </c>
       <c r="R2" t="n">
-        <v>6451200</v>
+        <v>6451303</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>1998-11-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>1998-11-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>080407371 / CHA PHAE / Enstaka-sparsam (1)  / OBJ.AREA:0,2 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,28 +762,356 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Lövskogslund /</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stone/rock on land</t>
+          <t>Gammal grov ek</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125887494</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92699</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>366</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storeryd , Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>483071</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6451216</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ödeshög</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stora Åby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Tomas Björkesten</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Tomas Björkesten</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>558478</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>200 m SO Knäpperyds gla tomt (08E0h37), Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483471</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6451303</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ödeshög</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Åby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1998-11-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1998-11-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>080407371 / ANTI CUR / Tämligen allmän (2)  / OBJ.AREA:0,2 ha</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lövskogslund /</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129954629</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Alboryds gamla tomt, Alboryds gamla tomt, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483508</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6451200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ödeshög</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Åby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
